--- a/webapp/public/templates/14. CẤU HÌNH TỰ ĐỘNG_QUÝ.xlsx
+++ b/webapp/public/templates/14. CẤU HÌNH TỰ ĐỘNG_QUÝ.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B31_QUY" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,58 +413,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Cột 1</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>Đơn vị</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>Tổng TB PTM</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>OneBSS→CPE</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cột 5</t>
+          <t>Tỷ lệ gửi (%)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cột 6</t>
+          <t>ONT tự động TC</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Cột 7</t>
+          <t>Tỷ lệ TC (%)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cột 8</t>
+          <t>ONT tự động lỗi</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Cột 9</t>
+          <t>Tỷ lệ lỗi (%)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cột 10</t>
+          <t>ONT nhân công</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ NC (%)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Cấp cáp tự động</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ cáp (%)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Cấp port tự động</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ port (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
         </is>
       </c>
     </row>

--- a/webapp/public/templates/14. CẤU HÌNH TỰ ĐỘNG_QUÝ.xlsx
+++ b/webapp/public/templates/14. CẤU HÌNH TỰ ĐỘNG_QUÝ.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,14 +496,1759 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>99.91%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3151</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>95.66%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>24.51%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>90.6%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Đức Hòa</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Hòa Thành</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>98.79</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>97.55</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>38.79</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>80.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Thủ Thừa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>98.61</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>23.61</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>98.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>91.15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>89.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>92.35</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>16.71</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>92.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>98.36</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>42.62</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>92.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Dương Minh Châu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>93.02</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>97.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Cần Đước</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>95.67</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>12.98</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>81.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Trụ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>97.89</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Bến Cầu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>96.63</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>93.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Cần Giuộc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>96.19</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>46.19</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>92.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Bến Lức</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>96.45</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>81.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Thạnh Hóa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>92.75</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>94.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Long An</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>94.78</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>11.65</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>92.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Đức Huệ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>99.34</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>95.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Trảng Bàng</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>96.12</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Vĩnh Hưng</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>94.87</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>98.72</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Thạnh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>15.57</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>89.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tầm Vu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>94.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Châu Thành</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>97.89</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>84.21</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>89.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Châu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>95.73</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>76.92</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>96.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Biên</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>92.94</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>47.06</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>98.82</t>
         </is>
       </c>
     </row>
